--- a/human_validation/judge/en/judge_D019_S005_P003__claude-sonnet-5.xlsx
+++ b/human_validation/judge/en/judge_D019_S005_P003__claude-sonnet-5.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -505,7 +506,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="8">
@@ -558,6 +559,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
